--- a/data/file_generation/input/data_57/2025-10-19_06_00_美职业_纽约城[东5]VS西雅图海湾人[西5]_标盘.xlsx
+++ b/data/file_generation/input/data_57/2025-10-19_06_00_美职业_纽约城[东5]VS西雅图海湾人[西5]_标盘.xlsx
@@ -16517,26 +16517,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C630B25-4633-413F-8E08-CA46E251C541}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6250A4C5-8E8E-4581-B2CC-0C3A92F87629}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7BCE5F9-64F4-4B20-BA71-4D2BE38AA6C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEF872DE-2197-4EE1-ADB0-70D75A0DEB89}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B7DFF28-EB85-43B5-A606-2B0D3BE47F06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83069A53-09DF-4F23-8661-4C83D362C513}"/>
 </file>